--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486938_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486938_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. VILA I GÓMEZ</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.144</v>
+        <v>0.0143</v>
       </c>
       <c r="E2" t="n">
-        <v>1.6964</v>
+        <v>1.1515</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.5524</v>
+        <v>-1.1372</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.5274</v>
+        <v>-0.08740000000000001</v>
       </c>
       <c r="H2" t="n">
-        <v>0.2593</v>
+        <v>-1.1162</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7866</v>
+        <v>1.0288</v>
       </c>
       <c r="J2" t="n">
-        <v>1.2898</v>
+        <v>1.3143</v>
       </c>
       <c r="K2" t="n">
-        <v>1.8687</v>
+        <v>0.0779</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.579</v>
+        <v>1.2365</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8171</v>
+        <v>-1.4017</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.6094</v>
+        <v>-1.194</v>
       </c>
       <c r="O2" t="n">
         <v>-0.2077</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2483</v>
+        <v>-0.5144</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4066</v>
+        <v>-0.1628</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1583</v>
+        <v>-0.3515</v>
       </c>
       <c r="V2" t="n">
-        <v>0.2177</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2177</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>A. VILA I GÓMEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0186</v>
+        <v>-0.2448</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.3459</v>
+        <v>1.278</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3272</v>
+        <v>-1.5228</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.8127</v>
+        <v>-0.5274</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2813</v>
+        <v>0.2593</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4686</v>
+        <v>-0.7866</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0271</v>
+        <v>1.2898</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.1455</v>
+        <v>1.8687</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1184</v>
+        <v>-0.579</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.7856</v>
+        <v>-1.8171</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1358</v>
+        <v>-1.6094</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3502</v>
+        <v>-0.2077</v>
       </c>
       <c r="P3" t="n">
-        <v>0.616</v>
+        <v>0.2053</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.2321</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.8481</v>
+        <v>0.2053</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2951</v>
+        <v>-0.1405</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6114</v>
+        <v>-0.0118</v>
       </c>
       <c r="U3" t="n">
-        <v>0.6837</v>
+        <v>-0.1287</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.117</v>
+        <v>0.2177</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.4189</v>
+        <v>0.2177</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.8208</v>
+        <v>-0.9975000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5239</v>
+        <v>0.3461</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.3447</v>
+        <v>-1.3436</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-6.2278</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.1162</v>
+        <v>-0.8306</v>
       </c>
       <c r="I4" t="n">
-        <v>1.0288</v>
+        <v>-5.3972</v>
       </c>
       <c r="J4" t="n">
-        <v>1.3143</v>
+        <v>-3.8374</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0779</v>
+        <v>0.6103</v>
       </c>
       <c r="L4" t="n">
-        <v>1.2365</v>
+        <v>-4.4477</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.4017</v>
+        <v>-2.3904</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.194</v>
+        <v>-1.4409</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2077</v>
+        <v>-0.9495</v>
       </c>
       <c r="P4" t="n">
-        <v>0.616</v>
+        <v>2.2588</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.616</v>
+        <v>2.2588</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3495</v>
+        <v>-0.9135</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7905</v>
+        <v>-0.531</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5590000000000001</v>
+        <v>-0.3824</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>3.885</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>4.7145</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.8295</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. CARRASCO MARTIN</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.6193</v>
+        <v>-1.719</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7393999999999999</v>
+        <v>-1.4903</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8799</v>
+        <v>-0.2287</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.0717</v>
+        <v>-2.8171</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.6373</v>
+        <v>-1.3331</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5656</v>
+        <v>-1.484</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.27</v>
+        <v>-0.8505</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1382</v>
+        <v>-0.0608</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1318</v>
+        <v>-0.7897</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8017</v>
+        <v>-1.9666</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.4991</v>
+        <v>-1.2723</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6974</v>
+        <v>-0.6943</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.2053</v>
+        <v>1.8481</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.0534</v>
       </c>
       <c r="S5" t="n">
-        <v>0.6578000000000001</v>
+        <v>-1.1217</v>
       </c>
       <c r="T5" t="n">
-        <v>0.736</v>
+        <v>-0.8061</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.07820000000000001</v>
+        <v>-0.3155</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.3716</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.3716</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.1604</v>
+        <v>-1.7481</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4908</v>
+        <v>-1.6011</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.6697</v>
+        <v>-0.147</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.2278</v>
+        <v>-0.8127</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8306</v>
+        <v>-1.2813</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.3972</v>
+        <v>0.4686</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.8374</v>
+        <v>-0.0271</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6103</v>
+        <v>-0.1455</v>
       </c>
       <c r="L6" t="n">
-        <v>-4.4477</v>
+        <v>0.1184</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.3904</v>
+        <v>-0.7856</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4409</v>
+        <v>-1.1358</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.9495</v>
+        <v>0.3502</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2588</v>
+        <v>0.616</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2588</v>
+        <v>1.8481</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.0764</v>
+        <v>0.5656</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3679</v>
+        <v>0.3562</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.7085</v>
+        <v>0.2094</v>
       </c>
       <c r="V6" t="n">
-        <v>3.885</v>
+        <v>-2.117</v>
       </c>
       <c r="W6" t="n">
-        <v>4.7145</v>
+        <v>-0.6982</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.8295</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>J. CARRASCO MARTIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2874</v>
+        <v>-2.2016</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1179</v>
+        <v>-1.2624</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.1695</v>
+        <v>-0.9392</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.8171</v>
+        <v>-2.0717</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3331</v>
+        <v>-2.6373</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.484</v>
+        <v>0.5656</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8505</v>
+        <v>-1.27</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0608</v>
+        <v>-1.1382</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.7897</v>
+        <v>-0.1318</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9666</v>
+        <v>-0.8017</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2723</v>
+        <v>-1.4991</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.6943</v>
+        <v>0.6974</v>
       </c>
       <c r="P7" t="n">
-        <v>1.8481</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.2053</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0534</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.69</v>
+        <v>0.0755</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.4337</v>
+        <v>0.213</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2563</v>
+        <v>-0.1374</v>
       </c>
       <c r="V7" t="n">
-        <v>0.3716</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3716</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. RENANE</t>
+          <t>I. VALERA COROMINAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2412</v>
+        <v>-4.279</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.6195</v>
+        <v>-3.6642</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6217</v>
+        <v>-0.6148</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.1893</v>
+        <v>-4.0991</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6133</v>
+        <v>-0.4706</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.576</v>
+        <v>-3.6285</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7828000000000001</v>
+        <v>-2.6636</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1908</v>
+        <v>0.6653</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.9737</v>
+        <v>-3.3289</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.4064</v>
+        <v>-1.4355</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.8041</v>
+        <v>-1.1358</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.6022999999999999</v>
+        <v>-0.2996</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.6694</v>
+        <v>2.0534</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.0801</v>
+        <v>-0.2053</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4107</v>
+        <v>2.2588</v>
       </c>
       <c r="S8" t="n">
-        <v>1.6175</v>
+        <v>-0.3565</v>
       </c>
       <c r="T8" t="n">
-        <v>1.2434</v>
+        <v>-0.09710000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3741</v>
+        <v>-0.2594</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.8768</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. VALERA COROMINAS</t>
+          <t>B. ALVAREZ TORRES</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-5.339</v>
+        <v>-4.8997</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6056</v>
+        <v>-4.0849</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7334000000000001</v>
+        <v>-0.8148</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.0991</v>
+        <v>-1.2152</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4706</v>
+        <v>-4.0778</v>
       </c>
       <c r="I9" t="n">
-        <v>-3.6285</v>
+        <v>2.8626</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.6636</v>
+        <v>0.4909</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6653</v>
+        <v>-2.4161</v>
       </c>
       <c r="L9" t="n">
-        <v>-3.3289</v>
+        <v>2.9071</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4355</v>
+        <v>-1.7061</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1358</v>
+        <v>-1.6616</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2996</v>
+        <v>-0.0445</v>
       </c>
       <c r="P9" t="n">
-        <v>2.0534</v>
+        <v>-2.6694</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2053</v>
+        <v>-4.3122</v>
       </c>
       <c r="R9" t="n">
-        <v>2.2588</v>
+        <v>1.6427</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.4165</v>
+        <v>-1.0151</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0385</v>
+        <v>-0.2637</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.378</v>
+        <v>-0.7514</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8768</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>B. ALVAREZ TORRES</t>
+          <t>P. RENANE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.4646</v>
+        <v>-5.7319</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2941</v>
+        <v>-3.6655</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1705</v>
+        <v>-2.0663</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2152</v>
+        <v>-3.1893</v>
       </c>
       <c r="H10" t="n">
-        <v>-4.0778</v>
+        <v>-0.6133</v>
       </c>
       <c r="I10" t="n">
-        <v>2.8626</v>
+        <v>-2.576</v>
       </c>
       <c r="J10" t="n">
-        <v>0.4909</v>
+        <v>-0.7828000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>-2.4161</v>
+        <v>1.1908</v>
       </c>
       <c r="L10" t="n">
-        <v>2.9071</v>
+        <v>-1.9737</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.7061</v>
+        <v>-2.4064</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6616</v>
+        <v>-1.8041</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0445</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="P10" t="n">
         <v>-2.6694</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.3122</v>
+        <v>-3.0801</v>
       </c>
       <c r="R10" t="n">
-        <v>1.6427</v>
+        <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.58</v>
+        <v>0.1269</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4729</v>
+        <v>0.1974</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.1071</v>
+        <v>-0.0706</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1270,10 +1270,10 @@
         <v>-21.8073</v>
       </c>
       <c r="E11" t="n">
-        <v>-12.9929</v>
+        <v>-12.9928</v>
       </c>
       <c r="F11" t="n">
-        <v>-8.8146</v>
+        <v>-8.814400000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-21.0477</v>
@@ -1285,13 +1285,13 @@
         <v>-8.9467</v>
       </c>
       <c r="J11" t="n">
-        <v>-6.336399999999999</v>
+        <v>-6.3364</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6524000000000001</v>
+        <v>0.6523999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-6.988799999999999</v>
+        <v>-6.9888</v>
       </c>
       <c r="M11" t="n">
         <v>-14.7111</v>
@@ -1306,22 +1306,22 @@
         <v>2.053499999999999</v>
       </c>
       <c r="Q11" t="n">
-        <v>-9.2403</v>
+        <v>-9.240300000000001</v>
       </c>
       <c r="R11" t="n">
         <v>11.2938</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.2937</v>
+        <v>-3.293699999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.1061</v>
+        <v>-1.1059</v>
       </c>
       <c r="U11" t="n">
-        <v>-2.1876</v>
+        <v>-2.1875</v>
       </c>
       <c r="V11" t="n">
-        <v>0.4804999999999995</v>
+        <v>0.4804999999999993</v>
       </c>
       <c r="W11" t="n">
         <v>3.6897</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>7.3216</v>
+        <v>7.332</v>
       </c>
       <c r="E12" t="n">
-        <v>4.0706</v>
+        <v>3.8614</v>
       </c>
       <c r="F12" t="n">
-        <v>3.251</v>
+        <v>3.4706</v>
       </c>
       <c r="G12" t="n">
         <v>5.1592</v>
@@ -1390,13 +1390,13 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>0.84</v>
+        <v>0.8504</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5384</v>
+        <v>0.3292</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3016</v>
+        <v>0.5213</v>
       </c>
       <c r="V12" t="n">
         <v>1.5277</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>D. DE LA RUA DE AGUSTIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.6698</v>
+        <v>5.7693</v>
       </c>
       <c r="E13" t="n">
-        <v>5.3411</v>
+        <v>4.6491</v>
       </c>
       <c r="F13" t="n">
-        <v>1.3286</v>
+        <v>1.1202</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5452</v>
+        <v>6.5503</v>
       </c>
       <c r="H13" t="n">
-        <v>2.9686</v>
+        <v>2.7639</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.4234</v>
+        <v>3.7864</v>
       </c>
       <c r="J13" t="n">
-        <v>3.0051</v>
+        <v>5.8309</v>
       </c>
       <c r="K13" t="n">
-        <v>2.9656</v>
+        <v>3.371</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0395</v>
+        <v>2.4599</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.4599</v>
+        <v>0.7194</v>
       </c>
       <c r="N13" t="n">
-        <v>0.003</v>
+        <v>-0.6071</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4629</v>
+        <v>1.3265</v>
       </c>
       <c r="P13" t="n">
-        <v>0.8214</v>
+        <v>-0.2053</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>-1.2321</v>
       </c>
       <c r="R13" t="n">
-        <v>0.8214</v>
+        <v>1.0267</v>
       </c>
       <c r="S13" t="n">
-        <v>2.4962</v>
+        <v>0.0136</v>
       </c>
       <c r="T13" t="n">
-        <v>2.336</v>
+        <v>0.0502</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1601</v>
+        <v>-0.0366</v>
       </c>
       <c r="V13" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.5893</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. DE LA RUA DE AGUSTIN</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.3404</v>
+        <v>5.2765</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4399</v>
+        <v>-0.1289</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9006</v>
+        <v>5.4053</v>
       </c>
       <c r="G14" t="n">
-        <v>6.5503</v>
+        <v>3.6898</v>
       </c>
       <c r="H14" t="n">
-        <v>2.7639</v>
+        <v>1.4112</v>
       </c>
       <c r="I14" t="n">
-        <v>3.7864</v>
+        <v>2.2787</v>
       </c>
       <c r="J14" t="n">
-        <v>5.8309</v>
+        <v>1.4683</v>
       </c>
       <c r="K14" t="n">
-        <v>3.371</v>
+        <v>0.3767</v>
       </c>
       <c r="L14" t="n">
-        <v>2.4599</v>
+        <v>1.0916</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7194</v>
+        <v>2.2215</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.6071</v>
+        <v>1.0345</v>
       </c>
       <c r="O14" t="n">
-        <v>1.3265</v>
+        <v>1.187</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.2053</v>
+        <v>0.2053</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.2321</v>
+        <v>-1.0267</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0267</v>
+        <v>1.2321</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.4152</v>
+        <v>1.3813</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.159</v>
+        <v>0.1277</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.2563</v>
+        <v>1.2536</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.5893</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.8755</v>
+        <v>5.1896</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.5473</v>
+        <v>3.7721</v>
       </c>
       <c r="F15" t="n">
-        <v>5.4228</v>
+        <v>1.4176</v>
       </c>
       <c r="G15" t="n">
-        <v>3.6898</v>
+        <v>2.5452</v>
       </c>
       <c r="H15" t="n">
-        <v>1.4112</v>
+        <v>2.9686</v>
       </c>
       <c r="I15" t="n">
-        <v>2.2787</v>
+        <v>-0.4234</v>
       </c>
       <c r="J15" t="n">
-        <v>1.4683</v>
+        <v>3.0051</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3767</v>
+        <v>2.9656</v>
       </c>
       <c r="L15" t="n">
-        <v>1.0916</v>
+        <v>0.0395</v>
       </c>
       <c r="M15" t="n">
-        <v>2.2215</v>
+        <v>-0.4599</v>
       </c>
       <c r="N15" t="n">
-        <v>1.0345</v>
+        <v>0.003</v>
       </c>
       <c r="O15" t="n">
-        <v>1.187</v>
+        <v>-0.4629</v>
       </c>
       <c r="P15" t="n">
-        <v>0.2053</v>
+        <v>0.8214</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.2321</v>
+        <v>0.8214</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9804</v>
+        <v>1.016</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2907</v>
+        <v>0.767</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2711</v>
+        <v>0.249</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.6982</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6982</v>
+        <v>0.8070000000000001</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.5668</v>
+        <v>3.8545</v>
       </c>
       <c r="E16" t="n">
         <v>1.2964</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2704</v>
+        <v>2.5581</v>
       </c>
       <c r="G16" t="n">
         <v>1.3487</v>
@@ -1702,13 +1702,13 @@
         <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>0.986</v>
+        <v>1.2737</v>
       </c>
       <c r="T16" t="n">
         <v>0.4066</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5794</v>
+        <v>0.8671</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8809</v>
+        <v>2.0124</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.4902</v>
+        <v>0.1375</v>
       </c>
       <c r="F17" t="n">
-        <v>1.371</v>
+        <v>1.875</v>
       </c>
       <c r="G17" t="n">
         <v>0.6651</v>
@@ -1780,13 +1780,13 @@
         <v>0.8214</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.086</v>
+        <v>0.0455</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5851</v>
+        <v>0.0425</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5009</v>
+        <v>0.003</v>
       </c>
       <c r="V17" t="n">
         <v>0.4805</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7361</v>
+        <v>0.6455</v>
       </c>
       <c r="E18" t="n">
-        <v>1.6458</v>
+        <v>1.4366</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9097</v>
+        <v>-0.7911</v>
       </c>
       <c r="G18" t="n">
         <v>0.1573</v>
@@ -1858,13 +1858,13 @@
         <v>0.4107</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3734</v>
+        <v>0.2828</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5733</v>
+        <v>0.3641</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1999</v>
+        <v>-0.0813</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.3399</v>
+        <v>0.509</v>
       </c>
       <c r="E19" t="n">
         <v>0.3166</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0233</v>
+        <v>0.1925</v>
       </c>
       <c r="G19" t="n">
         <v>1.0786</v>
@@ -1936,13 +1936,13 @@
         <v>0.2053</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.096</v>
+        <v>-0.9268999999999999</v>
       </c>
       <c r="T19" t="n">
         <v>-0.3294</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.7665999999999999</v>
+        <v>-0.5975</v>
       </c>
       <c r="V19" t="n">
         <v>1.1786</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R. GOMEZ BARRAL</t>
+          <t>G. GANTT</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.0128</v>
+        <v>-0.7821</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6392</v>
+        <v>-0.4325</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3737</v>
+        <v>-0.3497</v>
       </c>
       <c r="G20" t="n">
-        <v>1.0529</v>
+        <v>1.4029</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1977</v>
+        <v>0.7297</v>
       </c>
       <c r="I20" t="n">
-        <v>0.8552</v>
+        <v>0.6732</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0071</v>
+        <v>1.7179</v>
       </c>
       <c r="K20" t="n">
-        <v>1.3626</v>
+        <v>0.837</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6445</v>
+        <v>0.8809</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9542</v>
+        <v>-0.3151</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.1649</v>
+        <v>-0.1074</v>
       </c>
       <c r="O20" t="n">
-        <v>0.2107</v>
+        <v>-0.2077</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.6427</v>
+        <v>-1.2321</v>
       </c>
       <c r="Q20" t="n">
         <v>-2.2588</v>
       </c>
       <c r="R20" t="n">
-        <v>0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.423</v>
+        <v>0.2257</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3875</v>
+        <v>0.1084</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0355</v>
+        <v>0.1173</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. GANTT</t>
+          <t>R. GOMEZ BARRAL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.7567</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.0601</v>
+        <v>-0.2208</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6966</v>
+        <v>-0.7294</v>
       </c>
       <c r="G21" t="n">
-        <v>1.4029</v>
+        <v>1.0529</v>
       </c>
       <c r="H21" t="n">
-        <v>0.7297</v>
+        <v>0.1977</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6732</v>
+        <v>0.8552</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7179</v>
+        <v>2.0071</v>
       </c>
       <c r="K21" t="n">
-        <v>0.837</v>
+        <v>1.3626</v>
       </c>
       <c r="L21" t="n">
-        <v>0.8809</v>
+        <v>0.6445</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3151</v>
+        <v>-0.9542</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1074</v>
+        <v>-1.1649</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2077</v>
+        <v>0.2107</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.2321</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q21" t="n">
         <v>-2.2588</v>
       </c>
       <c r="R21" t="n">
-        <v>1.0267</v>
+        <v>0.616</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.7489</v>
+        <v>-0.3603</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5192</v>
+        <v>0.0309</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2297</v>
+        <v>-0.3912</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.1592</v>
+        <v>-2.2185</v>
       </c>
       <c r="E22" t="n">
         <v>-1.0995</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.0597</v>
+        <v>-1.119</v>
       </c>
       <c r="G22" t="n">
         <v>0.4459</v>
@@ -2170,13 +2170,13 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3998</v>
+        <v>-0.4591</v>
       </c>
       <c r="T22" t="n">
         <v>-0.1317</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.268</v>
+        <v>-0.3273</v>
       </c>
       <c r="V22" t="n">
         <v>-1.1786</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.9949</v>
+        <v>-3.436</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.4598</v>
+        <v>-4.7736</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4649</v>
+        <v>1.3376</v>
       </c>
       <c r="G23" t="n">
         <v>-3.0483</v>
@@ -2248,13 +2248,13 @@
         <v>0.8214</v>
       </c>
       <c r="S23" t="n">
-        <v>1.7865</v>
+        <v>1.3454</v>
       </c>
       <c r="T23" t="n">
-        <v>0.736</v>
+        <v>0.4222</v>
       </c>
       <c r="U23" t="n">
-        <v>1.0505</v>
+        <v>0.9232</v>
       </c>
       <c r="V23" t="n">
         <v>-1.5277</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>21.8074</v>
+        <v>23.2021</v>
       </c>
       <c r="E24" t="n">
-        <v>8.814299999999999</v>
+        <v>8.814400000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>12.9929</v>
+        <v>14.3877</v>
       </c>
       <c r="G24" t="n">
         <v>21.0476</v>
@@ -2311,7 +2311,7 @@
         <v>6.336399999999998</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6522000000000001</v>
+        <v>-0.6522000000000003</v>
       </c>
       <c r="O24" t="n">
         <v>6.9887</v>
@@ -2326,13 +2326,13 @@
         <v>9.240500000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>3.2936</v>
+        <v>4.688099999999999</v>
       </c>
       <c r="T24" t="n">
         <v>2.1877</v>
       </c>
       <c r="U24" t="n">
-        <v>1.1058</v>
+        <v>2.5006</v>
       </c>
       <c r="V24" t="n">
         <v>-0.4803999999999999</v>
